--- a/input_data/admin_data/SLV/_clean/wages-pre-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/wages-pre-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="257">
   <si>
     <t>year</t>
   </si>
@@ -37,6 +37,753 @@
   </si>
   <si>
     <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t/>
@@ -100,22 +847,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -123,7 +870,7 @@
         <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>5943366</v>
@@ -141,7 +888,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>5943366</v>
@@ -159,7 +906,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>5943366</v>
@@ -177,7 +924,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>5943366</v>
@@ -195,7 +942,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>5943366</v>
@@ -213,7 +960,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>5943366</v>
@@ -231,7 +978,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>5943366</v>
@@ -249,7 +996,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>5943366</v>
@@ -267,7 +1014,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>5943366</v>
@@ -285,7 +1032,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>5943366</v>
@@ -311,22 +1058,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>161</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
@@ -334,7 +1081,7 @@
         <v>2010</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="C2">
         <v>6068249</v>
@@ -352,7 +1099,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="C3">
         <v>6068249</v>
@@ -370,7 +1117,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="C4">
         <v>6068249</v>
@@ -388,7 +1135,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="C5">
         <v>6068249</v>
@@ -406,7 +1153,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="C6">
         <v>6068249</v>
@@ -424,7 +1171,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="C7">
         <v>6068249</v>
@@ -442,7 +1189,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="C8">
         <v>6068249</v>
@@ -460,7 +1207,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>157</v>
       </c>
       <c r="C9">
         <v>6068249</v>
@@ -478,7 +1225,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="C10">
         <v>6068249</v>
@@ -496,7 +1243,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="C11">
         <v>6068249</v>
@@ -522,22 +1269,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>175</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>177</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
@@ -545,7 +1292,7 @@
         <v>2012</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="C2">
         <v>6113975</v>
@@ -563,7 +1310,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>6113975</v>
@@ -581,7 +1328,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>168</v>
       </c>
       <c r="C4">
         <v>6113975</v>
@@ -599,7 +1346,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>169</v>
       </c>
       <c r="C5">
         <v>6113975</v>
@@ -617,7 +1364,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="C6">
         <v>6113975</v>
@@ -635,7 +1382,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="C7">
         <v>6113975</v>
@@ -653,7 +1400,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>172</v>
       </c>
       <c r="C8">
         <v>6113975</v>
@@ -671,7 +1418,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="C9">
         <v>6113975</v>
@@ -689,7 +1436,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>174</v>
       </c>
       <c r="C10">
         <v>6113975</v>
@@ -715,22 +1462,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>190</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2">
@@ -738,13 +1485,13 @@
         <v>2013</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>181</v>
       </c>
       <c r="C2">
         <v>6138839</v>
       </c>
       <c r="D2">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E2">
         <v>0.97289276123046875</v>
@@ -756,13 +1503,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>182</v>
       </c>
       <c r="C3">
         <v>6138839</v>
       </c>
       <c r="D3">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E3">
         <v>0.97424709796905518</v>
@@ -774,13 +1521,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C4">
         <v>6138839</v>
       </c>
       <c r="D4">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E4">
         <v>0.97784191370010376</v>
@@ -792,13 +1539,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>6138839</v>
       </c>
       <c r="D5">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E5">
         <v>0.9950181245803833</v>
@@ -810,13 +1557,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="C6">
         <v>6138839</v>
       </c>
       <c r="D6">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E6">
         <v>0.99870824813842773</v>
@@ -828,13 +1575,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="C7">
         <v>6138839</v>
       </c>
       <c r="D7">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E7">
         <v>0.99969702959060669</v>
@@ -846,13 +1593,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="C8">
         <v>6138839</v>
       </c>
       <c r="D8">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E8">
         <v>0.99993419647216797</v>
@@ -864,13 +1611,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="C9">
         <v>6138839</v>
       </c>
       <c r="D9">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E9">
         <v>0.99996399879455566</v>
@@ -882,13 +1629,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="C10">
         <v>6138839</v>
       </c>
       <c r="D10">
-        <v>314.92227172851562</v>
+        <v>314.92227172851563</v>
       </c>
       <c r="E10">
         <v>0.99999904632568359</v>
@@ -908,22 +1655,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>195</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>205</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>206</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2">
@@ -931,7 +1678,7 @@
         <v>2014</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>196</v>
       </c>
       <c r="C2">
         <v>6162955</v>
@@ -949,7 +1696,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="C3">
         <v>6162955</v>
@@ -967,7 +1714,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>198</v>
       </c>
       <c r="C4">
         <v>6162955</v>
@@ -985,7 +1732,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>199</v>
       </c>
       <c r="C5">
         <v>6162955</v>
@@ -1003,7 +1750,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="C6">
         <v>6162955</v>
@@ -1021,7 +1768,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="C7">
         <v>6162955</v>
@@ -1039,7 +1786,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>202</v>
       </c>
       <c r="C8">
         <v>6162955</v>
@@ -1057,7 +1804,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>203</v>
       </c>
       <c r="C9">
         <v>6162955</v>
@@ -1075,7 +1822,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>204</v>
       </c>
       <c r="C10">
         <v>6162955</v>
@@ -1101,22 +1848,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>223</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2">
@@ -1124,7 +1871,7 @@
         <v>2015</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>211</v>
       </c>
       <c r="C2">
         <v>6183676</v>
@@ -1142,7 +1889,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="C3">
         <v>6183676</v>
@@ -1160,7 +1907,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>213</v>
       </c>
       <c r="C4">
         <v>6183676</v>
@@ -1178,7 +1925,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>214</v>
       </c>
       <c r="C5">
         <v>6183676</v>
@@ -1196,7 +1943,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>215</v>
       </c>
       <c r="C6">
         <v>6183676</v>
@@ -1214,7 +1961,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="C7">
         <v>6183676</v>
@@ -1232,7 +1979,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="C8">
         <v>6183676</v>
@@ -1250,7 +1997,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>218</v>
       </c>
       <c r="C9">
         <v>6183676</v>
@@ -1268,7 +2015,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>219</v>
       </c>
       <c r="C10">
         <v>6183676</v>
@@ -1286,7 +2033,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="C11">
         <v>6183676</v>
@@ -1312,22 +2059,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>237</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>238</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>239</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2">
@@ -1335,13 +2082,13 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>227</v>
       </c>
       <c r="C2">
         <v>6200800</v>
       </c>
       <c r="D2">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E2">
         <v>0.96577620506286621</v>
@@ -1353,13 +2100,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>228</v>
       </c>
       <c r="C3">
         <v>6200800</v>
       </c>
       <c r="D3">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E3">
         <v>0.96695071458816528</v>
@@ -1371,13 +2118,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>229</v>
       </c>
       <c r="C4">
         <v>6200800</v>
       </c>
       <c r="D4">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E4">
         <v>0.97109532356262207</v>
@@ -1389,13 +2136,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="C5">
         <v>6200800</v>
       </c>
       <c r="D5">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E5">
         <v>0.99311429262161255</v>
@@ -1407,13 +2154,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>231</v>
       </c>
       <c r="C6">
         <v>6200800</v>
       </c>
       <c r="D6">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E6">
         <v>0.99829262495040894</v>
@@ -1425,13 +2172,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>232</v>
       </c>
       <c r="C7">
         <v>6200800</v>
       </c>
       <c r="D7">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E7">
         <v>0.9996299147605896</v>
@@ -1443,13 +2190,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>233</v>
       </c>
       <c r="C8">
         <v>6200800</v>
       </c>
       <c r="D8">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E8">
         <v>0.99992680549621582</v>
@@ -1461,13 +2208,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>234</v>
       </c>
       <c r="C9">
         <v>6200800</v>
       </c>
       <c r="D9">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E9">
         <v>0.99995642900466919</v>
@@ -1479,13 +2226,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>235</v>
       </c>
       <c r="C10">
         <v>6200800</v>
       </c>
       <c r="D10">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E10">
         <v>0.99999630451202393</v>
@@ -1497,13 +2244,13 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="C11">
         <v>6200800</v>
       </c>
       <c r="D11">
-        <v>414.84707641601562</v>
+        <v>414.84707641601563</v>
       </c>
       <c r="E11">
         <v>0.99999886751174927</v>
@@ -1523,22 +2270,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -1546,7 +2293,7 @@
         <v>2017</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6213533</v>
@@ -1564,7 +2311,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>244</v>
       </c>
       <c r="C3">
         <v>6213533</v>
@@ -1582,7 +2329,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>245</v>
       </c>
       <c r="C4">
         <v>6213533</v>
@@ -1600,7 +2347,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="C5">
         <v>6213533</v>
@@ -1618,7 +2365,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>247</v>
       </c>
       <c r="C6">
         <v>6213533</v>
@@ -1636,7 +2383,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>248</v>
       </c>
       <c r="C7">
         <v>6213533</v>
@@ -1654,7 +2401,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="C8">
         <v>6213533</v>
@@ -1672,7 +2419,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="C9">
         <v>6213533</v>
@@ -1690,7 +2437,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="C10">
         <v>6213533</v>
@@ -1708,7 +2455,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>6213533</v>
@@ -1734,22 +2481,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
@@ -1757,13 +2504,13 @@
         <v>2001</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>5968060</v>
       </c>
       <c r="D2">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E2">
         <v>0.97199761867523193</v>
@@ -1775,13 +2522,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>5968060</v>
       </c>
       <c r="D3">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E3">
         <v>0.97491896152496338</v>
@@ -1793,13 +2540,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>5968060</v>
       </c>
       <c r="D4">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E4">
         <v>0.9808925986289978</v>
@@ -1811,13 +2558,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>5968060</v>
       </c>
       <c r="D5">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E5">
         <v>0.99738472700119019</v>
@@ -1829,13 +2576,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>5968060</v>
       </c>
       <c r="D6">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E6">
         <v>0.99949163198471069</v>
@@ -1847,13 +2594,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>5968060</v>
       </c>
       <c r="D7">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E7">
         <v>0.99991267919540405</v>
@@ -1865,13 +2612,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>5968060</v>
       </c>
       <c r="D8">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E8">
         <v>0.9999842643737793</v>
@@ -1883,13 +2630,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>5968060</v>
       </c>
       <c r="D9">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E9">
         <v>0.999991774559021</v>
@@ -1901,13 +2648,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>5968060</v>
       </c>
       <c r="D10">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E10">
         <v>0.9999995231628418</v>
@@ -1919,13 +2666,13 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>5968060</v>
       </c>
       <c r="D11">
-        <v>229.48318481445312</v>
+        <v>229.48318481445313</v>
       </c>
       <c r="E11">
         <v>0.99999982118606567</v>
@@ -1945,22 +2692,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
@@ -1968,7 +2715,7 @@
         <v>2002</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C2">
         <v>5986631</v>
@@ -1986,7 +2733,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C3">
         <v>5986631</v>
@@ -2004,7 +2751,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>5986631</v>
@@ -2022,7 +2769,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C5">
         <v>5986631</v>
@@ -2040,7 +2787,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C6">
         <v>5986631</v>
@@ -2058,7 +2805,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C7">
         <v>5986631</v>
@@ -2076,7 +2823,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C8">
         <v>5986631</v>
@@ -2094,7 +2841,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C9">
         <v>5986631</v>
@@ -2112,7 +2859,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>5986631</v>
@@ -2138,22 +2885,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2">
@@ -2161,7 +2908,7 @@
         <v>2003</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="C2">
         <v>5998599</v>
@@ -2179,7 +2926,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C3">
         <v>5998599</v>
@@ -2197,7 +2944,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C4">
         <v>5998599</v>
@@ -2215,7 +2962,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C5">
         <v>5998599</v>
@@ -2233,7 +2980,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>5998599</v>
@@ -2251,7 +2998,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>5998599</v>
@@ -2269,7 +3016,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C8">
         <v>5998599</v>
@@ -2287,7 +3034,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C9">
         <v>5998599</v>
@@ -2305,7 +3052,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C10">
         <v>5998599</v>
@@ -2331,22 +3078,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2">
@@ -2354,13 +3101,13 @@
         <v>2004</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>6004671</v>
       </c>
       <c r="D2">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E2">
         <v>0.96806567907333374</v>
@@ -2372,13 +3119,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>6004671</v>
       </c>
       <c r="D3">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E3">
         <v>0.97190040349960327</v>
@@ -2390,13 +3137,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>6004671</v>
       </c>
       <c r="D4">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E4">
         <v>0.97897803783416748</v>
@@ -2408,13 +3155,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="C5">
         <v>6004671</v>
       </c>
       <c r="D5">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E5">
         <v>0.99717605113983154</v>
@@ -2426,13 +3173,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="C6">
         <v>6004671</v>
       </c>
       <c r="D6">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E6">
         <v>0.99943125247955322</v>
@@ -2444,13 +3191,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="C7">
         <v>6004671</v>
       </c>
       <c r="D7">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E7">
         <v>0.99990308284759521</v>
@@ -2462,13 +3209,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="C8">
         <v>6004671</v>
       </c>
       <c r="D8">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E8">
         <v>0.9999840259552002</v>
@@ -2480,13 +3227,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>6004671</v>
       </c>
       <c r="D9">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E9">
         <v>0.99999052286148071</v>
@@ -2498,13 +3245,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>6004671</v>
       </c>
       <c r="D10">
-        <v>252.43045043945312</v>
+        <v>252.43045043945313</v>
       </c>
       <c r="E10">
         <v>0.99999964237213135</v>
@@ -2524,22 +3271,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
@@ -2547,7 +3294,7 @@
         <v>2005</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="C2">
         <v>6005578</v>
@@ -2565,7 +3312,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C3">
         <v>6005578</v>
@@ -2583,7 +3330,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="C4">
         <v>6005578</v>
@@ -2601,7 +3348,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="C5">
         <v>6005578</v>
@@ -2619,7 +3366,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="C6">
         <v>6005578</v>
@@ -2637,7 +3384,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="C7">
         <v>6005578</v>
@@ -2655,7 +3402,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="C8">
         <v>6005578</v>
@@ -2673,7 +3420,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="C9">
         <v>6005578</v>
@@ -2691,7 +3438,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="C10">
         <v>6005578</v>
@@ -2709,7 +3456,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C11">
         <v>6005578</v>
@@ -2735,22 +3482,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2">
@@ -2758,13 +3505,13 @@
         <v>2006</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>6002319</v>
       </c>
       <c r="D2">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E2">
         <v>0.96240085363388062</v>
@@ -2776,13 +3523,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="C3">
         <v>6002319</v>
       </c>
       <c r="D3">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E3">
         <v>0.96693128347396851</v>
@@ -2794,13 +3541,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="C4">
         <v>6002319</v>
       </c>
       <c r="D4">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E4">
         <v>0.97507262229919434</v>
@@ -2812,13 +3559,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="C5">
         <v>6002319</v>
       </c>
       <c r="D5">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E5">
         <v>0.99639022350311279</v>
@@ -2830,13 +3577,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="C6">
         <v>6002319</v>
       </c>
       <c r="D6">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E6">
         <v>0.99921178817749023</v>
@@ -2848,13 +3595,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="C7">
         <v>6002319</v>
       </c>
       <c r="D7">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E7">
         <v>0.99984824657440186</v>
@@ -2866,13 +3613,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="C8">
         <v>6002319</v>
       </c>
       <c r="D8">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E8">
         <v>0.99997466802597046</v>
@@ -2884,13 +3631,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <v>6002319</v>
       </c>
       <c r="D9">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E9">
         <v>0.9999840259552002</v>
@@ -2902,13 +3649,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>111</v>
       </c>
       <c r="C10">
         <v>6002319</v>
       </c>
       <c r="D10">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E10">
         <v>0.99999785423278809</v>
@@ -2920,13 +3667,13 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="C11">
         <v>6002319</v>
       </c>
       <c r="D11">
-        <v>342.91812133789062</v>
+        <v>342.91812133789063</v>
       </c>
       <c r="E11">
         <v>0.99999868869781494</v>
@@ -2946,22 +3693,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2">
@@ -2969,13 +3716,13 @@
         <v>2007</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="C2">
         <v>6009824</v>
       </c>
       <c r="D2">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E2">
         <v>0.95716977119445801</v>
@@ -2987,13 +3734,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="C3">
         <v>6009824</v>
       </c>
       <c r="D3">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E3">
         <v>0.96256715059280396</v>
@@ -3005,13 +3752,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="C4">
         <v>6009824</v>
       </c>
       <c r="D4">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E4">
         <v>0.9713473916053772</v>
@@ -3023,13 +3770,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="C5">
         <v>6009824</v>
       </c>
       <c r="D5">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E5">
         <v>0.99594897031784058</v>
@@ -3041,13 +3788,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="C6">
         <v>6009824</v>
       </c>
       <c r="D6">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E6">
         <v>0.99912875890731812</v>
@@ -3059,13 +3806,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="C7">
         <v>6009824</v>
       </c>
       <c r="D7">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E7">
         <v>0.99983125925064087</v>
@@ -3077,13 +3824,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>125</v>
       </c>
       <c r="C8">
         <v>6009824</v>
       </c>
       <c r="D8">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E8">
         <v>0.9999728798866272</v>
@@ -3095,13 +3842,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="C9">
         <v>6009824</v>
       </c>
       <c r="D9">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E9">
         <v>0.9999852180480957</v>
@@ -3113,13 +3860,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="C10">
         <v>6009824</v>
       </c>
       <c r="D10">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E10">
         <v>0.99999868869781494</v>
@@ -3131,13 +3878,13 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="C11">
         <v>6009824</v>
       </c>
       <c r="D11">
-        <v>353.39138793945312</v>
+        <v>353.39138793945313</v>
       </c>
       <c r="E11">
         <v>0.99999934434890747</v>
@@ -3157,22 +3904,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2">
@@ -3180,7 +3927,7 @@
         <v>2009</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>6048279</v>
@@ -3198,7 +3945,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>136</v>
       </c>
       <c r="C3">
         <v>6048279</v>
@@ -3216,7 +3963,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="C4">
         <v>6048279</v>
@@ -3234,7 +3981,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="C5">
         <v>6048279</v>
@@ -3252,7 +3999,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>6048279</v>
@@ -3270,7 +4017,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>6048279</v>
@@ -3288,7 +4035,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>141</v>
       </c>
       <c r="C8">
         <v>6048279</v>
@@ -3306,7 +4053,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="C9">
         <v>6048279</v>
@@ -3324,7 +4071,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="C10">
         <v>6048279</v>

--- a/input_data/admin_data/SLV/_clean/wages-pre-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/wages-pre-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="257">
   <si>
     <t>year</t>
   </si>
@@ -847,22 +847,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -870,7 +870,7 @@
         <v>2000</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>5943366</v>
@@ -888,7 +888,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>5943366</v>
@@ -906,7 +906,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>5943366</v>
@@ -924,7 +924,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>5943366</v>
@@ -942,7 +942,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>5943366</v>
@@ -960,7 +960,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>5943366</v>
@@ -978,7 +978,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>5943366</v>
@@ -996,7 +996,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>5943366</v>
@@ -1014,7 +1014,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>5943366</v>
@@ -1032,7 +1032,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>5943366</v>
@@ -1058,22 +1058,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>149</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>163</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -1081,7 +1081,7 @@
         <v>2010</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6068249</v>
@@ -1099,7 +1099,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6068249</v>
@@ -1117,7 +1117,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6068249</v>
@@ -1135,7 +1135,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6068249</v>
@@ -1153,7 +1153,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6068249</v>
@@ -1171,7 +1171,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6068249</v>
@@ -1189,7 +1189,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6068249</v>
@@ -1207,7 +1207,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6068249</v>
@@ -1225,7 +1225,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6068249</v>
@@ -1243,7 +1243,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>6068249</v>
@@ -1269,22 +1269,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>165</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>175</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>177</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -1292,7 +1292,7 @@
         <v>2012</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6113975</v>
@@ -1310,7 +1310,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6113975</v>
@@ -1328,7 +1328,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6113975</v>
@@ -1346,7 +1346,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6113975</v>
@@ -1364,7 +1364,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6113975</v>
@@ -1382,7 +1382,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6113975</v>
@@ -1400,7 +1400,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6113975</v>
@@ -1418,7 +1418,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6113975</v>
@@ -1436,7 +1436,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6113975</v>
@@ -1462,22 +1462,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>190</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>191</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -1485,13 +1485,13 @@
         <v>2013</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6138839</v>
       </c>
       <c r="D2">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E2">
         <v>0.97289276123046875</v>
@@ -1503,13 +1503,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6138839</v>
       </c>
       <c r="D3">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E3">
         <v>0.97424709796905518</v>
@@ -1521,13 +1521,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6138839</v>
       </c>
       <c r="D4">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E4">
         <v>0.97784191370010376</v>
@@ -1539,13 +1539,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6138839</v>
       </c>
       <c r="D5">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E5">
         <v>0.9950181245803833</v>
@@ -1557,13 +1557,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6138839</v>
       </c>
       <c r="D6">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E6">
         <v>0.99870824813842773</v>
@@ -1575,13 +1575,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6138839</v>
       </c>
       <c r="D7">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E7">
         <v>0.99969702959060669</v>
@@ -1593,13 +1593,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6138839</v>
       </c>
       <c r="D8">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E8">
         <v>0.99993419647216797</v>
@@ -1611,13 +1611,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6138839</v>
       </c>
       <c r="D9">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E9">
         <v>0.99996399879455566</v>
@@ -1629,13 +1629,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6138839</v>
       </c>
       <c r="D10">
-        <v>314.92227172851563</v>
+        <v>314.92227172851562</v>
       </c>
       <c r="E10">
         <v>0.99999904632568359</v>
@@ -1655,22 +1655,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>207</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>208</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -1678,7 +1678,7 @@
         <v>2014</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6162955</v>
@@ -1696,7 +1696,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6162955</v>
@@ -1714,7 +1714,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6162955</v>
@@ -1732,7 +1732,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6162955</v>
@@ -1750,7 +1750,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6162955</v>
@@ -1768,7 +1768,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6162955</v>
@@ -1786,7 +1786,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6162955</v>
@@ -1804,7 +1804,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6162955</v>
@@ -1822,7 +1822,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6162955</v>
@@ -1848,22 +1848,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -1871,7 +1871,7 @@
         <v>2015</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6183676</v>
@@ -1889,7 +1889,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6183676</v>
@@ -1907,7 +1907,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6183676</v>
@@ -1925,7 +1925,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6183676</v>
@@ -1943,7 +1943,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6183676</v>
@@ -1961,7 +1961,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6183676</v>
@@ -1979,7 +1979,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6183676</v>
@@ -1997,7 +1997,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6183676</v>
@@ -2015,7 +2015,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6183676</v>
@@ -2033,7 +2033,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>6183676</v>
@@ -2059,22 +2059,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -2082,13 +2082,13 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6200800</v>
       </c>
       <c r="D2">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E2">
         <v>0.96577620506286621</v>
@@ -2100,13 +2100,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6200800</v>
       </c>
       <c r="D3">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E3">
         <v>0.96695071458816528</v>
@@ -2118,13 +2118,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6200800</v>
       </c>
       <c r="D4">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E4">
         <v>0.97109532356262207</v>
@@ -2136,13 +2136,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6200800</v>
       </c>
       <c r="D5">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E5">
         <v>0.99311429262161255</v>
@@ -2154,13 +2154,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6200800</v>
       </c>
       <c r="D6">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E6">
         <v>0.99829262495040894</v>
@@ -2172,13 +2172,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6200800</v>
       </c>
       <c r="D7">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E7">
         <v>0.9996299147605896</v>
@@ -2190,13 +2190,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6200800</v>
       </c>
       <c r="D8">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E8">
         <v>0.99992680549621582</v>
@@ -2208,13 +2208,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6200800</v>
       </c>
       <c r="D9">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E9">
         <v>0.99995642900466919</v>
@@ -2226,13 +2226,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6200800</v>
       </c>
       <c r="D10">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E10">
         <v>0.99999630451202393</v>
@@ -2244,13 +2244,13 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>6200800</v>
       </c>
       <c r="D11">
-        <v>414.84707641601563</v>
+        <v>414.84707641601562</v>
       </c>
       <c r="E11">
         <v>0.99999886751174927</v>
@@ -2311,7 +2311,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6213533</v>
@@ -2329,7 +2329,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6213533</v>
@@ -2347,7 +2347,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6213533</v>
@@ -2365,7 +2365,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6213533</v>
@@ -2383,7 +2383,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6213533</v>
@@ -2401,7 +2401,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6213533</v>
@@ -2419,7 +2419,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6213533</v>
@@ -2437,7 +2437,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6213533</v>
@@ -2481,22 +2481,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -2504,13 +2504,13 @@
         <v>2001</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>5968060</v>
       </c>
       <c r="D2">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E2">
         <v>0.97199761867523193</v>
@@ -2522,13 +2522,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>5968060</v>
       </c>
       <c r="D3">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E3">
         <v>0.97491896152496338</v>
@@ -2540,13 +2540,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>5968060</v>
       </c>
       <c r="D4">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E4">
         <v>0.9808925986289978</v>
@@ -2558,13 +2558,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>5968060</v>
       </c>
       <c r="D5">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E5">
         <v>0.99738472700119019</v>
@@ -2576,13 +2576,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>5968060</v>
       </c>
       <c r="D6">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E6">
         <v>0.99949163198471069</v>
@@ -2594,13 +2594,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>5968060</v>
       </c>
       <c r="D7">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E7">
         <v>0.99991267919540405</v>
@@ -2612,13 +2612,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>5968060</v>
       </c>
       <c r="D8">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E8">
         <v>0.9999842643737793</v>
@@ -2630,13 +2630,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>5968060</v>
       </c>
       <c r="D9">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E9">
         <v>0.999991774559021</v>
@@ -2648,13 +2648,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>5968060</v>
       </c>
       <c r="D10">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E10">
         <v>0.9999995231628418</v>
@@ -2666,13 +2666,13 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>5968060</v>
       </c>
       <c r="D11">
-        <v>229.48318481445313</v>
+        <v>229.48318481445312</v>
       </c>
       <c r="E11">
         <v>0.99999982118606567</v>
@@ -2692,22 +2692,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>53</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>54</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -2715,7 +2715,7 @@
         <v>2002</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>5986631</v>
@@ -2733,7 +2733,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>5986631</v>
@@ -2751,7 +2751,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>5986631</v>
@@ -2769,7 +2769,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>5986631</v>
@@ -2787,7 +2787,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>5986631</v>
@@ -2805,7 +2805,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>5986631</v>
@@ -2823,7 +2823,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>5986631</v>
@@ -2841,7 +2841,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>5986631</v>
@@ -2859,7 +2859,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>5986631</v>
@@ -2885,22 +2885,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -2908,7 +2908,7 @@
         <v>2003</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>5998599</v>
@@ -2926,7 +2926,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>5998599</v>
@@ -2944,7 +2944,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>5998599</v>
@@ -2962,7 +2962,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>5998599</v>
@@ -2980,7 +2980,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>5998599</v>
@@ -2998,7 +2998,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>5998599</v>
@@ -3016,7 +3016,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>5998599</v>
@@ -3034,7 +3034,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>5998599</v>
@@ -3052,7 +3052,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>5998599</v>
@@ -3078,22 +3078,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>83</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>84</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3101,13 +3101,13 @@
         <v>2004</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6004671</v>
       </c>
       <c r="D2">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E2">
         <v>0.96806567907333374</v>
@@ -3119,13 +3119,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6004671</v>
       </c>
       <c r="D3">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E3">
         <v>0.97190040349960327</v>
@@ -3137,13 +3137,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6004671</v>
       </c>
       <c r="D4">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E4">
         <v>0.97897803783416748</v>
@@ -3155,13 +3155,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6004671</v>
       </c>
       <c r="D5">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E5">
         <v>0.99717605113983154</v>
@@ -3173,13 +3173,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6004671</v>
       </c>
       <c r="D6">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E6">
         <v>0.99943125247955322</v>
@@ -3191,13 +3191,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6004671</v>
       </c>
       <c r="D7">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E7">
         <v>0.99990308284759521</v>
@@ -3209,13 +3209,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6004671</v>
       </c>
       <c r="D8">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E8">
         <v>0.9999840259552002</v>
@@ -3227,13 +3227,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6004671</v>
       </c>
       <c r="D9">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E9">
         <v>0.99999052286148071</v>
@@ -3245,13 +3245,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6004671</v>
       </c>
       <c r="D10">
-        <v>252.43045043945313</v>
+        <v>252.43045043945312</v>
       </c>
       <c r="E10">
         <v>0.99999964237213135</v>
@@ -3271,22 +3271,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>97</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>100</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3294,7 +3294,7 @@
         <v>2005</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6005578</v>
@@ -3312,7 +3312,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6005578</v>
@@ -3330,7 +3330,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6005578</v>
@@ -3348,7 +3348,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6005578</v>
@@ -3366,7 +3366,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6005578</v>
@@ -3384,7 +3384,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6005578</v>
@@ -3402,7 +3402,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6005578</v>
@@ -3420,7 +3420,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6005578</v>
@@ -3438,7 +3438,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6005578</v>
@@ -3456,7 +3456,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>6005578</v>
@@ -3482,22 +3482,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>102</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>114</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3505,13 +3505,13 @@
         <v>2006</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6002319</v>
       </c>
       <c r="D2">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E2">
         <v>0.96240085363388062</v>
@@ -3523,13 +3523,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6002319</v>
       </c>
       <c r="D3">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E3">
         <v>0.96693128347396851</v>
@@ -3541,13 +3541,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6002319</v>
       </c>
       <c r="D4">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E4">
         <v>0.97507262229919434</v>
@@ -3559,13 +3559,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6002319</v>
       </c>
       <c r="D5">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E5">
         <v>0.99639022350311279</v>
@@ -3577,13 +3577,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6002319</v>
       </c>
       <c r="D6">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E6">
         <v>0.99921178817749023</v>
@@ -3595,13 +3595,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6002319</v>
       </c>
       <c r="D7">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E7">
         <v>0.99984824657440186</v>
@@ -3613,13 +3613,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6002319</v>
       </c>
       <c r="D8">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E8">
         <v>0.99997466802597046</v>
@@ -3631,13 +3631,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6002319</v>
       </c>
       <c r="D9">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E9">
         <v>0.9999840259552002</v>
@@ -3649,13 +3649,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6002319</v>
       </c>
       <c r="D10">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E10">
         <v>0.99999785423278809</v>
@@ -3667,13 +3667,13 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>6002319</v>
       </c>
       <c r="D11">
-        <v>342.91812133789063</v>
+        <v>342.91812133789062</v>
       </c>
       <c r="E11">
         <v>0.99999868869781494</v>
@@ -3693,22 +3693,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>131</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>132</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3716,13 +3716,13 @@
         <v>2007</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6009824</v>
       </c>
       <c r="D2">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E2">
         <v>0.95716977119445801</v>
@@ -3734,13 +3734,13 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6009824</v>
       </c>
       <c r="D3">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E3">
         <v>0.96256715059280396</v>
@@ -3752,13 +3752,13 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6009824</v>
       </c>
       <c r="D4">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E4">
         <v>0.9713473916053772</v>
@@ -3770,13 +3770,13 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6009824</v>
       </c>
       <c r="D5">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E5">
         <v>0.99594897031784058</v>
@@ -3788,13 +3788,13 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6009824</v>
       </c>
       <c r="D6">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E6">
         <v>0.99912875890731812</v>
@@ -3806,13 +3806,13 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6009824</v>
       </c>
       <c r="D7">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E7">
         <v>0.99983125925064087</v>
@@ -3824,13 +3824,13 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6009824</v>
       </c>
       <c r="D8">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E8">
         <v>0.9999728798866272</v>
@@ -3842,13 +3842,13 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6009824</v>
       </c>
       <c r="D9">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E9">
         <v>0.9999852180480957</v>
@@ -3860,13 +3860,13 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6009824</v>
       </c>
       <c r="D10">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E10">
         <v>0.99999868869781494</v>
@@ -3878,13 +3878,13 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>252</v>
       </c>
       <c r="C11">
         <v>6009824</v>
       </c>
       <c r="D11">
-        <v>353.39138793945313</v>
+        <v>353.39138793945312</v>
       </c>
       <c r="E11">
         <v>0.99999934434890747</v>
@@ -3904,22 +3904,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="C1" t="s">
-        <v>144</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>146</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>147</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3927,7 +3927,7 @@
         <v>2009</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="C2">
         <v>6048279</v>
@@ -3945,7 +3945,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="C3">
         <v>6048279</v>
@@ -3963,7 +3963,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>252</v>
       </c>
       <c r="C4">
         <v>6048279</v>
@@ -3981,7 +3981,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="C5">
         <v>6048279</v>
@@ -3999,7 +3999,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="C6">
         <v>6048279</v>
@@ -4017,7 +4017,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>252</v>
       </c>
       <c r="C7">
         <v>6048279</v>
@@ -4035,7 +4035,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>252</v>
       </c>
       <c r="C8">
         <v>6048279</v>
@@ -4053,7 +4053,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>6048279</v>
@@ -4071,7 +4071,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="C10">
         <v>6048279</v>

--- a/input_data/admin_data/SLV/_clean/wages-pre-SLV.xlsx
+++ b/input_data/admin_data/SLV/_clean/wages-pre-SLV.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="257">
   <si>
     <t>year</t>
   </si>
